--- a/Config/Datas/__enums__.xlsx
+++ b/Config/Datas/__enums__.xlsx
@@ -1,51 +1,61 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28227"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace2\luban_examples\MiniTemplate\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57E1AAA0-A88D-4E41-AC05-256E9DB382D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
   <si>
+    <t>##</t>
+  </si>
+  <si>
+    <t>full_name</t>
+  </si>
+  <si>
+    <t>flags</t>
+  </si>
+  <si>
+    <t>unique</t>
+  </si>
+  <si>
+    <t>group</t>
+  </si>
+  <si>
+    <t>comment</t>
+  </si>
+  <si>
+    <t>tags</t>
+  </si>
+  <si>
+    <t>*items</t>
+  </si>
+  <si>
     <t>##var</t>
   </si>
   <si>
-    <t>full_name</t>
-  </si>
-  <si>
-    <t>flags</t>
-  </si>
-  <si>
-    <t>unique</t>
-  </si>
-  <si>
-    <t>group</t>
-  </si>
-  <si>
-    <t>comment</t>
-  </si>
-  <si>
-    <t>tags</t>
-  </si>
-  <si>
-    <t>*items</t>
-  </si>
-  <si>
     <t>name</t>
   </si>
   <si>
@@ -53,9 +63,6 @@
   </si>
   <si>
     <t>value</t>
-  </si>
-  <si>
-    <t>##</t>
   </si>
   <si>
     <t>全名(包含模块和名字)</t>
@@ -82,8 +89,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -92,13 +105,151 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -107,12 +258,198 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79995117038483843"/>
+        <fgColor theme="9" tint="0.799951170384838"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -135,9 +472,251 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -149,23 +728,67 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -423,14 +1046,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:L3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="2"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="20.875" customWidth="1"/>
@@ -443,7 +1066,7 @@
     <col min="11" max="11" width="15.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -465,17 +1088,17 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -484,13 +1107,13 @@
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>5</v>
@@ -499,14 +1122,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="99" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" ht="99" customHeight="1" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -533,8 +1156,8 @@
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Config/Datas/__enums__.xlsx
+++ b/Config/Datas/__enums__.xlsx
@@ -1,257 +1,177 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17655" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>full_name</t>
-  </si>
-  <si>
-    <t>flags</t>
-  </si>
-  <si>
-    <t>unique</t>
-  </si>
-  <si>
-    <t>group</t>
-  </si>
-  <si>
-    <t>comment</t>
-  </si>
-  <si>
-    <t>tags</t>
-  </si>
-  <si>
-    <t>*items</t>
-  </si>
-  <si>
-    <t>##var</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>alias</t>
-  </si>
-  <si>
-    <t>value</t>
-  </si>
-  <si>
-    <t>全名(包含模块和名字)</t>
-  </si>
-  <si>
-    <t>是否为位标记枚举（即每个枚举项为位标记数据，例如System.IO.FileMode,填数据时可以为READ|WRITE这样)</t>
-  </si>
-  <si>
-    <t>枚举项是否唯一</t>
-  </si>
-  <si>
-    <t>枚举名</t>
-  </si>
-  <si>
-    <t>别名</t>
-  </si>
-  <si>
-    <t>值</t>
-  </si>
-  <si>
-    <t>注释</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="20">
     <font>
-      <sz val="11"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <b val="1"/>
+      <color theme="3"/>
       <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <b val="1"/>
       <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
+      <b val="1"/>
       <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
+      <b val="1"/>
       <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
       <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
       <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
       <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
       <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
       <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
       <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="34">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -449,7 +369,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -570,169 +490,216 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -786,11 +753,74 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1050,114 +1080,260 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:L3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L9"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="2"/>
   <cols>
-    <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="20.875" customWidth="1"/>
-    <col min="4" max="5" width="14.125" customWidth="1"/>
-    <col min="6" max="6" width="9.375" customWidth="1"/>
-    <col min="7" max="7" width="5" customWidth="1"/>
-    <col min="8" max="8" width="13.5" customWidth="1"/>
-    <col min="9" max="9" width="5.25" customWidth="1"/>
-    <col min="10" max="10" width="12.125" customWidth="1"/>
-    <col min="11" max="11" width="15.125" customWidth="1"/>
+    <col width="19" customWidth="1" style="4" min="2" max="2"/>
+    <col width="20.875" customWidth="1" style="4" min="3" max="3"/>
+    <col width="14.125" customWidth="1" style="4" min="4" max="5"/>
+    <col width="9.375" customWidth="1" style="4" min="6" max="6"/>
+    <col width="5" customWidth="1" style="4" min="7" max="7"/>
+    <col width="13.5" customWidth="1" style="4" min="8" max="8"/>
+    <col width="5.25" customWidth="1" style="4" min="9" max="9"/>
+    <col width="12.125" customWidth="1" style="4" min="10" max="10"/>
+    <col width="15.125" customWidth="1" style="4" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>full_name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>flags</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>*items</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="n"/>
+      <c r="J1" s="5" t="n"/>
+      <c r="K1" s="5" t="n"/>
+      <c r="L1" s="6" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n"/>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>alias</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="99" customHeight="1" s="4">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>全名(包含模块和名字)</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>是否为位标记枚举（即每个枚举项为位标记数据，例如System.IO.FileMode,填数据时可以为READ|WRITE这样)</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>枚举项是否唯一</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="n"/>
+      <c r="F3" s="1" t="n"/>
+      <c r="G3" s="1" t="n"/>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>枚举名</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>别名</t>
+        </is>
+      </c>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t>注释</t>
+        </is>
+      </c>
+      <c r="L3" s="1" t="n"/>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>demo.ESkillLoadoutSlotType</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>技能装配槽类型</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>未指定</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>LeftClick</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>左键槽0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>RightClick</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>右键槽1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Dash</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>冲刺槽2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>OtherActive</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>其他主动槽3-7</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" ht="99" customHeight="1" spans="1:12">
-      <c r="A3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L3" s="1"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>被动槽</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/Config/Datas/__enums__.xlsx
+++ b/Config/Datas/__enums__.xlsx
@@ -1,299 +1,177 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17655" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>full_name</t>
-  </si>
-  <si>
-    <t>flags</t>
-  </si>
-  <si>
-    <t>unique</t>
-  </si>
-  <si>
-    <t>group</t>
-  </si>
-  <si>
-    <t>comment</t>
-  </si>
-  <si>
-    <t>tags</t>
-  </si>
-  <si>
-    <t>*items</t>
-  </si>
-  <si>
-    <t>##var</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>alias</t>
-  </si>
-  <si>
-    <t>value</t>
-  </si>
-  <si>
-    <t>全名(包含模块和名字)</t>
-  </si>
-  <si>
-    <t>是否为位标记枚举（即每个枚举项为位标记数据，例如System.IO.FileMode,填数据时可以为READ|WRITE这样)</t>
-  </si>
-  <si>
-    <t>枚举项是否唯一</t>
-  </si>
-  <si>
-    <t>枚举名</t>
-  </si>
-  <si>
-    <t>别名</t>
-  </si>
-  <si>
-    <t>值</t>
-  </si>
-  <si>
-    <t>注释</t>
-  </si>
-  <si>
-    <t>demo.ESkillLoadoutSlotType</t>
-  </si>
-  <si>
-    <t>技能装配槽类型</t>
-  </si>
-  <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t>未指定</t>
-  </si>
-  <si>
-    <t>LeftClick</t>
-  </si>
-  <si>
-    <t>左键槽0</t>
-  </si>
-  <si>
-    <t>RightClick</t>
-  </si>
-  <si>
-    <t>右键槽1</t>
-  </si>
-  <si>
-    <t>Dash</t>
-  </si>
-  <si>
-    <t>冲刺槽2</t>
-  </si>
-  <si>
-    <t>OtherActive</t>
-  </si>
-  <si>
-    <t>其他主动槽3-7</t>
-  </si>
-  <si>
-    <t>Passive</t>
-  </si>
-  <si>
-    <t>被动槽</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="20">
     <font>
-      <sz val="11"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="34">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -491,7 +369,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -636,170 +514,190 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -855,11 +753,74 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1119,178 +1080,483 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:L9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L24"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="19" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.875" style="1" customWidth="1"/>
-    <col min="4" max="5" width="14.125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="5" style="1" customWidth="1"/>
-    <col min="8" max="8" width="13.5" style="1" customWidth="1"/>
-    <col min="9" max="9" width="5.25" style="1" customWidth="1"/>
-    <col min="10" max="10" width="12.125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="15.125" style="1" customWidth="1"/>
+    <col width="19" customWidth="1" style="1" min="2" max="2"/>
+    <col width="20.875" customWidth="1" style="1" min="3" max="3"/>
+    <col width="14.125" customWidth="1" style="1" min="4" max="5"/>
+    <col width="9.375" customWidth="1" style="1" min="6" max="6"/>
+    <col width="5" customWidth="1" style="1" min="7" max="7"/>
+    <col width="13.5" customWidth="1" style="1" min="8" max="8"/>
+    <col width="5.25" customWidth="1" style="1" min="9" max="9"/>
+    <col width="12.125" customWidth="1" style="1" min="10" max="10"/>
+    <col width="15.125" customWidth="1" style="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="2" t="s">
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>full_name</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>flags</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>*items</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="n"/>
+      <c r="J1" s="4" t="n"/>
+      <c r="K1" s="4" t="n"/>
+      <c r="L1" s="5" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>alias</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="99" customHeight="1" s="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>全名(包含模块和名字)</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>是否为位标记枚举（即每个枚举项为位标记数据，例如System.IO.FileMode,填数据时可以为READ|WRITE这样)</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>枚举项是否唯一</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>枚举名</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>别名</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>注释</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>demo.ESkillLoadoutSlotType</t>
+        </is>
+      </c>
+      <c r="F4" s="0" t="inlineStr">
+        <is>
+          <t>技能装配槽类型</t>
+        </is>
+      </c>
+      <c r="H4" s="0" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J4" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="K4" s="0" t="inlineStr">
+        <is>
+          <t>未指定</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="H5" s="0" t="inlineStr">
+        <is>
+          <t>LeftClick</t>
+        </is>
+      </c>
+      <c r="J5" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="K5" s="0" t="inlineStr">
+        <is>
+          <t>左键槽0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="H6" s="0" t="inlineStr">
+        <is>
+          <t>RightClick</t>
+        </is>
+      </c>
+      <c r="J6" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="K6" s="0" t="inlineStr">
+        <is>
+          <t>右键槽1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="H7" s="0" t="inlineStr">
+        <is>
+          <t>Dash</t>
+        </is>
+      </c>
+      <c r="J7" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="K7" s="0" t="inlineStr">
+        <is>
+          <t>冲刺槽2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="H8" s="0" t="inlineStr">
+        <is>
+          <t>OtherActive</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="K8" s="0" t="inlineStr">
+        <is>
+          <t>其他主动槽3-7</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="H9" s="0" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="K9" s="0" t="inlineStr">
+        <is>
+          <t>被动槽</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>demo.EJingYuanType</t>
+        </is>
+      </c>
+      <c r="H10" s="0" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="0" t="inlineStr">
+        <is>
+          <t>无精型</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="H11" s="0" t="inlineStr">
+        <is>
+          <t>OrcCommon</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="0" t="inlineStr">
+        <is>
+          <t>兽人精元</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="H12" s="0" t="inlineStr">
+        <is>
+          <t>OrcElite</t>
+        </is>
+      </c>
+      <c r="J12" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" s="0" t="inlineStr">
+        <is>
+          <t>兽人精英精元</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="H13" s="0" t="inlineStr">
+        <is>
+          <t>SignAries</t>
+        </is>
+      </c>
+      <c r="J13" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" s="0" t="inlineStr">
+        <is>
+          <t>白羊座精元</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="H14" s="0" t="inlineStr">
+        <is>
+          <t>SignTaurus</t>
+        </is>
+      </c>
+      <c r="J14" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="K14" s="0" t="inlineStr">
+        <is>
+          <t>金牛座精元</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="H15" s="0" t="inlineStr">
+        <is>
+          <t>SignGemini</t>
+        </is>
+      </c>
+      <c r="J15" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="K15" s="0" t="inlineStr">
+        <is>
+          <t>双子座精元</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="H16" s="0" t="inlineStr">
+        <is>
+          <t>SignCancer</t>
+        </is>
+      </c>
+      <c r="J16" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="K16" s="0" t="inlineStr">
+        <is>
+          <t>巨蟹座精元</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="H17" s="0" t="inlineStr">
+        <is>
+          <t>SignLeo</t>
+        </is>
+      </c>
+      <c r="J17" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="5"/>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="2" t="s">
+      <c r="K17" s="0" t="inlineStr">
+        <is>
+          <t>狮子座精元</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="H18" s="0" t="inlineStr">
+        <is>
+          <t>SignVirgo</t>
+        </is>
+      </c>
+      <c r="J18" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2" t="s">
+      <c r="K18" s="0" t="inlineStr">
+        <is>
+          <t>处女座精元</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="H19" s="0" t="inlineStr">
+        <is>
+          <t>SignLibra</t>
+        </is>
+      </c>
+      <c r="J19" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="K19" s="0" t="inlineStr">
+        <is>
+          <t>天秤座精元</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="H20" s="0" t="inlineStr">
+        <is>
+          <t>SignScorpio</t>
+        </is>
+      </c>
+      <c r="J20" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K20" s="0" t="inlineStr">
+        <is>
+          <t>天蝎座精元</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="H21" s="0" t="inlineStr">
+        <is>
+          <t>SignSagittarius</t>
+        </is>
+      </c>
+      <c r="J21" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" ht="99" customHeight="1" spans="1:12">
-      <c r="A3" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="K21" s="0" t="inlineStr">
+        <is>
+          <t>射手座精元</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="H22" s="0" t="inlineStr">
+        <is>
+          <t>SignCapricorn</t>
+        </is>
+      </c>
+      <c r="J22" s="0" t="n">
         <v>12</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="K22" s="0" t="inlineStr">
+        <is>
+          <t>摩羯座精元</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="H23" s="0" t="inlineStr">
+        <is>
+          <t>SignAquarius</t>
+        </is>
+      </c>
+      <c r="J23" s="0" t="n">
         <v>13</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="K23" s="0" t="inlineStr">
+        <is>
+          <t>水瓶座精元</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="H24" s="0" t="inlineStr">
+        <is>
+          <t>SignPisces</t>
+        </is>
+      </c>
+      <c r="J24" s="0" t="n">
         <v>14</v>
       </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="L3" s="2"/>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="H5" t="s">
-        <v>23</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="H6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="K6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="H7" t="s">
-        <v>27</v>
-      </c>
-      <c r="J7">
-        <v>3</v>
-      </c>
-      <c r="K7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="H8" t="s">
-        <v>29</v>
-      </c>
-      <c r="J8">
-        <v>4</v>
-      </c>
-      <c r="K8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="H9" t="s">
-        <v>31</v>
-      </c>
-      <c r="J9">
-        <v>5</v>
-      </c>
-      <c r="K9" t="s">
-        <v>32</v>
+      <c r="K24" s="0" t="inlineStr">
+        <is>
+          <t>双鱼座精元</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1298,7 +1564,6 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/Config/Datas/__enums__.xlsx
+++ b/Config/Datas/__enums__.xlsx
@@ -1085,7 +1085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="19" customWidth="1" style="1" min="2" max="2"/>
@@ -1329,236 +1329,6 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" s="0" t="inlineStr">
-        <is>
-          <t>demo.EJingYuanType</t>
-        </is>
-      </c>
-      <c r="H10" s="0" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="J10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="0" t="inlineStr">
-        <is>
-          <t>无精型</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="H11" s="0" t="inlineStr">
-        <is>
-          <t>OrcCommon</t>
-        </is>
-      </c>
-      <c r="J11" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" s="0" t="inlineStr">
-        <is>
-          <t>兽人精元</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="H12" s="0" t="inlineStr">
-        <is>
-          <t>OrcElite</t>
-        </is>
-      </c>
-      <c r="J12" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="K12" s="0" t="inlineStr">
-        <is>
-          <t>兽人精英精元</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="H13" s="0" t="inlineStr">
-        <is>
-          <t>SignAries</t>
-        </is>
-      </c>
-      <c r="J13" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="K13" s="0" t="inlineStr">
-        <is>
-          <t>白羊座精元</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="H14" s="0" t="inlineStr">
-        <is>
-          <t>SignTaurus</t>
-        </is>
-      </c>
-      <c r="J14" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="K14" s="0" t="inlineStr">
-        <is>
-          <t>金牛座精元</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="H15" s="0" t="inlineStr">
-        <is>
-          <t>SignGemini</t>
-        </is>
-      </c>
-      <c r="J15" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="K15" s="0" t="inlineStr">
-        <is>
-          <t>双子座精元</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="H16" s="0" t="inlineStr">
-        <is>
-          <t>SignCancer</t>
-        </is>
-      </c>
-      <c r="J16" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="K16" s="0" t="inlineStr">
-        <is>
-          <t>巨蟹座精元</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="H17" s="0" t="inlineStr">
-        <is>
-          <t>SignLeo</t>
-        </is>
-      </c>
-      <c r="J17" s="0" t="n">
-        <v>7</v>
-      </c>
-      <c r="K17" s="0" t="inlineStr">
-        <is>
-          <t>狮子座精元</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="H18" s="0" t="inlineStr">
-        <is>
-          <t>SignVirgo</t>
-        </is>
-      </c>
-      <c r="J18" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="K18" s="0" t="inlineStr">
-        <is>
-          <t>处女座精元</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="H19" s="0" t="inlineStr">
-        <is>
-          <t>SignLibra</t>
-        </is>
-      </c>
-      <c r="J19" s="0" t="n">
-        <v>9</v>
-      </c>
-      <c r="K19" s="0" t="inlineStr">
-        <is>
-          <t>天秤座精元</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="H20" s="0" t="inlineStr">
-        <is>
-          <t>SignScorpio</t>
-        </is>
-      </c>
-      <c r="J20" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="K20" s="0" t="inlineStr">
-        <is>
-          <t>天蝎座精元</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="H21" s="0" t="inlineStr">
-        <is>
-          <t>SignSagittarius</t>
-        </is>
-      </c>
-      <c r="J21" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="K21" s="0" t="inlineStr">
-        <is>
-          <t>射手座精元</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="H22" s="0" t="inlineStr">
-        <is>
-          <t>SignCapricorn</t>
-        </is>
-      </c>
-      <c r="J22" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="K22" s="0" t="inlineStr">
-        <is>
-          <t>摩羯座精元</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="H23" s="0" t="inlineStr">
-        <is>
-          <t>SignAquarius</t>
-        </is>
-      </c>
-      <c r="J23" s="0" t="n">
-        <v>13</v>
-      </c>
-      <c r="K23" s="0" t="inlineStr">
-        <is>
-          <t>水瓶座精元</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="H24" s="0" t="inlineStr">
-        <is>
-          <t>SignPisces</t>
-        </is>
-      </c>
-      <c r="J24" s="0" t="n">
-        <v>14</v>
-      </c>
-      <c r="K24" s="0" t="inlineStr">
-        <is>
-          <t>双鱼座精元</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>

--- a/Config/Datas/__enums__.xlsx
+++ b/Config/Datas/__enums__.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17655" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1085,7 +1085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L74"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="19" customWidth="1" style="1" min="2" max="2"/>
@@ -1329,6 +1329,1119 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>demo.EItemTag</t>
+        </is>
+      </c>
+      <c r="F10" s="0" t="inlineStr">
+        <is>
+          <t>??????</t>
+        </is>
+      </c>
+      <c r="H10" s="0" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="0" t="inlineStr">
+        <is>
+          <t>???</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="0" t="n"/>
+      <c r="F11" s="0" t="n"/>
+      <c r="H11" s="0" t="inlineStr">
+        <is>
+          <t>Gift</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="0" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="0" t="n"/>
+      <c r="F12" s="0" t="n"/>
+      <c r="H12" s="0" t="inlineStr">
+        <is>
+          <t>PartGear</t>
+        </is>
+      </c>
+      <c r="J12" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" s="0" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="0" t="n"/>
+      <c r="F13" s="0" t="n"/>
+      <c r="H13" s="0" t="inlineStr">
+        <is>
+          <t>HumanWeapon</t>
+        </is>
+      </c>
+      <c r="J13" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="K13" s="0" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="0" t="n"/>
+      <c r="F14" s="0" t="n"/>
+      <c r="H14" s="0" t="inlineStr">
+        <is>
+          <t>HumanTool</t>
+        </is>
+      </c>
+      <c r="J14" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="K14" s="0" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="0" t="n"/>
+      <c r="F15" s="0" t="n"/>
+      <c r="H15" s="0" t="inlineStr">
+        <is>
+          <t>Pocket</t>
+        </is>
+      </c>
+      <c r="J15" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="K15" s="0" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="0" t="n"/>
+      <c r="F16" s="0" t="n"/>
+      <c r="H16" s="0" t="inlineStr">
+        <is>
+          <t>Insertion</t>
+        </is>
+      </c>
+      <c r="J16" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="K16" s="0" t="inlineStr">
+        <is>
+          <t>???</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="0" t="n"/>
+      <c r="F17" s="0" t="n"/>
+      <c r="H17" s="0" t="inlineStr">
+        <is>
+          <t>Plant</t>
+        </is>
+      </c>
+      <c r="J17" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="K17" s="0" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="0" t="n"/>
+      <c r="F18" s="0" t="n"/>
+      <c r="H18" s="0" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="J18" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="K18" s="0" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="0" t="n"/>
+      <c r="F19" s="0" t="n"/>
+      <c r="H19" s="0" t="inlineStr">
+        <is>
+          <t>Potion</t>
+        </is>
+      </c>
+      <c r="J19" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="K19" s="0" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="0" t="n"/>
+      <c r="F20" s="0" t="n"/>
+      <c r="H20" s="0" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="J20" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="K20" s="0" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="0" t="n"/>
+      <c r="F21" s="0" t="n"/>
+      <c r="H21" s="0" t="inlineStr">
+        <is>
+          <t>Dismantleable</t>
+        </is>
+      </c>
+      <c r="J21" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="K21" s="0" t="inlineStr">
+        <is>
+          <t>???</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="0" t="n"/>
+      <c r="F22" s="0" t="n"/>
+      <c r="H22" s="0" t="inlineStr">
+        <is>
+          <t>Jingyuan</t>
+        </is>
+      </c>
+      <c r="J22" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="K22" s="0" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="0" t="n"/>
+      <c r="F23" s="0" t="n"/>
+      <c r="H23" s="0" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="J23" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="K23" s="0" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="0" t="n"/>
+      <c r="F24" s="0" t="n"/>
+      <c r="H24" s="0" t="inlineStr">
+        <is>
+          <t>Big</t>
+        </is>
+      </c>
+      <c r="J24" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="K24" s="0" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="0" t="n"/>
+      <c r="F25" s="0" t="n"/>
+      <c r="H25" s="0" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="J25" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="K25" s="0" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="0" t="n"/>
+      <c r="F26" s="0" t="n"/>
+      <c r="H26" s="0" t="inlineStr">
+        <is>
+          <t>Wood</t>
+        </is>
+      </c>
+      <c r="J26" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="K26" s="0" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="0" t="n"/>
+      <c r="F27" s="0" t="n"/>
+      <c r="H27" s="0" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="J27" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="K27" s="0" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="0" t="n"/>
+      <c r="F28" s="0" t="n"/>
+      <c r="H28" s="0" t="inlineStr">
+        <is>
+          <t>Alchemy</t>
+        </is>
+      </c>
+      <c r="J28" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="K28" s="0" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="0" t="n"/>
+      <c r="F29" s="0" t="n"/>
+      <c r="H29" s="0" t="inlineStr">
+        <is>
+          <t>Fuel</t>
+        </is>
+      </c>
+      <c r="J29" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="K29" s="0" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="0" t="n"/>
+      <c r="F30" s="0" t="n"/>
+      <c r="H30" s="0" t="inlineStr">
+        <is>
+          <t>Fiber</t>
+        </is>
+      </c>
+      <c r="J30" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="K30" s="0" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="0" t="n"/>
+      <c r="F31" s="0" t="n"/>
+      <c r="H31" s="0" t="inlineStr">
+        <is>
+          <t>Stone</t>
+        </is>
+      </c>
+      <c r="J31" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="K31" s="0" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="0" t="n"/>
+      <c r="F32" s="0" t="n"/>
+      <c r="H32" s="0" t="inlineStr">
+        <is>
+          <t>Glass</t>
+        </is>
+      </c>
+      <c r="J32" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="K32" s="0" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="0" t="n"/>
+      <c r="F33" s="0" t="n"/>
+      <c r="H33" s="0" t="inlineStr">
+        <is>
+          <t>Clay</t>
+        </is>
+      </c>
+      <c r="J33" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="K33" s="0" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="0" t="n"/>
+      <c r="F34" s="0" t="n"/>
+      <c r="H34" s="0" t="inlineStr">
+        <is>
+          <t>Ceramic</t>
+        </is>
+      </c>
+      <c r="J34" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="K34" s="0" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="0" t="n"/>
+      <c r="F35" s="0" t="n"/>
+      <c r="H35" s="0" t="inlineStr">
+        <is>
+          <t>Luxury</t>
+        </is>
+      </c>
+      <c r="J35" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="K35" s="0" t="inlineStr">
+        <is>
+          <t>???</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="0" t="n"/>
+      <c r="F36" s="0" t="n"/>
+      <c r="H36" s="0" t="inlineStr">
+        <is>
+          <t>Craft</t>
+        </is>
+      </c>
+      <c r="J36" s="0" t="n">
+        <v>27</v>
+      </c>
+      <c r="K36" s="0" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="0" t="n"/>
+      <c r="F37" s="0" t="n"/>
+      <c r="H37" s="0" t="inlineStr">
+        <is>
+          <t>Ore</t>
+        </is>
+      </c>
+      <c r="J37" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="K37" s="0" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="0" t="n"/>
+      <c r="F38" s="0" t="n"/>
+      <c r="H38" s="0" t="inlineStr">
+        <is>
+          <t>Metal</t>
+        </is>
+      </c>
+      <c r="J38" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="K38" s="0" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="0" t="n"/>
+      <c r="F39" s="0" t="n"/>
+      <c r="H39" s="0" t="inlineStr">
+        <is>
+          <t>Precious</t>
+        </is>
+      </c>
+      <c r="J39" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="K39" s="0" t="inlineStr">
+        <is>
+          <t>???</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="0" t="n"/>
+      <c r="F40" s="0" t="n"/>
+      <c r="H40" s="0" t="inlineStr">
+        <is>
+          <t>Textile</t>
+        </is>
+      </c>
+      <c r="J40" s="0" t="n">
+        <v>31</v>
+      </c>
+      <c r="K40" s="0" t="inlineStr">
+        <is>
+          <t>???</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="0" t="n"/>
+      <c r="F41" s="0" t="n"/>
+      <c r="H41" s="0" t="inlineStr">
+        <is>
+          <t>Leather</t>
+        </is>
+      </c>
+      <c r="J41" s="0" t="n">
+        <v>32</v>
+      </c>
+      <c r="K41" s="0" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="0" t="n"/>
+      <c r="F42" s="0" t="n"/>
+      <c r="H42" s="0" t="inlineStr">
+        <is>
+          <t>Bone</t>
+        </is>
+      </c>
+      <c r="J42" s="0" t="n">
+        <v>33</v>
+      </c>
+      <c r="K42" s="0" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="0" t="n"/>
+      <c r="F43" s="0" t="n"/>
+      <c r="H43" s="0" t="inlineStr">
+        <is>
+          <t>Dye</t>
+        </is>
+      </c>
+      <c r="J43" s="0" t="n">
+        <v>34</v>
+      </c>
+      <c r="K43" s="0" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="0" t="n"/>
+      <c r="F44" s="0" t="n"/>
+      <c r="H44" s="0" t="inlineStr">
+        <is>
+          <t>Glue</t>
+        </is>
+      </c>
+      <c r="J44" s="0" t="n">
+        <v>35</v>
+      </c>
+      <c r="K44" s="0" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="0" t="n"/>
+      <c r="F45" s="0" t="n"/>
+      <c r="H45" s="0" t="inlineStr">
+        <is>
+          <t>Latex</t>
+        </is>
+      </c>
+      <c r="J45" s="0" t="n">
+        <v>36</v>
+      </c>
+      <c r="K45" s="0" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="0" t="n"/>
+      <c r="F46" s="0" t="n"/>
+      <c r="H46" s="0" t="inlineStr">
+        <is>
+          <t>Exotic</t>
+        </is>
+      </c>
+      <c r="J46" s="0" t="n">
+        <v>37</v>
+      </c>
+      <c r="K46" s="0" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="0" t="n"/>
+      <c r="F47" s="0" t="n"/>
+      <c r="H47" s="0" t="inlineStr">
+        <is>
+          <t>Loot</t>
+        </is>
+      </c>
+      <c r="J47" s="0" t="n">
+        <v>38</v>
+      </c>
+      <c r="K47" s="0" t="inlineStr">
+        <is>
+          <t>???</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="0" t="n"/>
+      <c r="F48" s="0" t="n"/>
+      <c r="H48" s="0" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="J48" s="0" t="n">
+        <v>39</v>
+      </c>
+      <c r="K48" s="0" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="0" t="n"/>
+      <c r="F49" s="0" t="n"/>
+      <c r="H49" s="0" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="J49" s="0" t="n">
+        <v>40</v>
+      </c>
+      <c r="K49" s="0" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="0" t="n"/>
+      <c r="F50" s="0" t="n"/>
+      <c r="H50" s="0" t="inlineStr">
+        <is>
+          <t>Gel</t>
+        </is>
+      </c>
+      <c r="J50" s="0" t="n">
+        <v>41</v>
+      </c>
+      <c r="K50" s="0" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="0" t="n"/>
+      <c r="F51" s="0" t="n"/>
+      <c r="H51" s="0" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="J51" s="0" t="n">
+        <v>42</v>
+      </c>
+      <c r="K51" s="0" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="0" t="n"/>
+      <c r="F52" s="0" t="n"/>
+      <c r="H52" s="0" t="inlineStr">
+        <is>
+          <t>Wax</t>
+        </is>
+      </c>
+      <c r="J52" s="0" t="n">
+        <v>43</v>
+      </c>
+      <c r="K52" s="0" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="0" t="n"/>
+      <c r="F53" s="0" t="n"/>
+      <c r="H53" s="0" t="inlineStr">
+        <is>
+          <t>Toy</t>
+        </is>
+      </c>
+      <c r="J53" s="0" t="n">
+        <v>44</v>
+      </c>
+      <c r="K53" s="0" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="0" t="n"/>
+      <c r="F54" s="0" t="n"/>
+      <c r="H54" s="0" t="inlineStr">
+        <is>
+          <t>Decor</t>
+        </is>
+      </c>
+      <c r="J54" s="0" t="n">
+        <v>45</v>
+      </c>
+      <c r="K54" s="0" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="0" t="n"/>
+      <c r="F55" s="0" t="n"/>
+      <c r="H55" s="0" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="J55" s="0" t="n">
+        <v>46</v>
+      </c>
+      <c r="K55" s="0" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="0" t="n"/>
+      <c r="F56" s="0" t="n"/>
+      <c r="H56" s="0" t="inlineStr">
+        <is>
+          <t>Study</t>
+        </is>
+      </c>
+      <c r="J56" s="0" t="n">
+        <v>47</v>
+      </c>
+      <c r="K56" s="0" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="0" t="n"/>
+      <c r="F57" s="0" t="n"/>
+      <c r="H57" s="0" t="inlineStr">
+        <is>
+          <t>Church</t>
+        </is>
+      </c>
+      <c r="J57" s="0" t="n">
+        <v>48</v>
+      </c>
+      <c r="K57" s="0" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="0" t="n"/>
+      <c r="F58" s="0" t="n"/>
+      <c r="H58" s="0" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="J58" s="0" t="n">
+        <v>49</v>
+      </c>
+      <c r="K58" s="0" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="0" t="n"/>
+      <c r="F59" s="0" t="n"/>
+      <c r="H59" s="0" t="inlineStr">
+        <is>
+          <t>Forest</t>
+        </is>
+      </c>
+      <c r="J59" s="0" t="n">
+        <v>50</v>
+      </c>
+      <c r="K59" s="0" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="0" t="n"/>
+      <c r="F60" s="0" t="n"/>
+      <c r="H60" s="0" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="J60" s="0" t="n">
+        <v>51</v>
+      </c>
+      <c r="K60" s="0" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="0" t="n"/>
+      <c r="F61" s="0" t="n"/>
+      <c r="H61" s="0" t="inlineStr">
+        <is>
+          <t>Facility</t>
+        </is>
+      </c>
+      <c r="J61" s="0" t="n">
+        <v>52</v>
+      </c>
+      <c r="K61" s="0" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="0" t="n"/>
+      <c r="F62" s="0" t="n"/>
+      <c r="H62" s="0" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="J62" s="0" t="n">
+        <v>53</v>
+      </c>
+      <c r="K62" s="0" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="0" t="n"/>
+      <c r="F63" s="0" t="n"/>
+      <c r="H63" s="0" t="inlineStr">
+        <is>
+          <t>Salvage</t>
+        </is>
+      </c>
+      <c r="J63" s="0" t="n">
+        <v>54</v>
+      </c>
+      <c r="K63" s="0" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="0" t="n"/>
+      <c r="F64" s="0" t="n"/>
+      <c r="H64" s="0" t="inlineStr">
+        <is>
+          <t>Dew</t>
+        </is>
+      </c>
+      <c r="J64" s="0" t="n">
+        <v>55</v>
+      </c>
+      <c r="K64" s="0" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="0" t="n"/>
+      <c r="F65" s="0" t="n"/>
+      <c r="H65" s="0" t="inlineStr">
+        <is>
+          <t>Fairy</t>
+        </is>
+      </c>
+      <c r="J65" s="0" t="n">
+        <v>56</v>
+      </c>
+      <c r="K65" s="0" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="0" t="n"/>
+      <c r="F66" s="0" t="n"/>
+      <c r="H66" s="0" t="inlineStr">
+        <is>
+          <t>Charge</t>
+        </is>
+      </c>
+      <c r="J66" s="0" t="n">
+        <v>57</v>
+      </c>
+      <c r="K66" s="0" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="0" t="n"/>
+      <c r="F67" s="0" t="n"/>
+      <c r="H67" s="0" t="inlineStr">
+        <is>
+          <t>PremiumEssenceDrop</t>
+        </is>
+      </c>
+      <c r="J67" s="0" t="n">
+        <v>58</v>
+      </c>
+      <c r="K67" s="0" t="inlineStr">
+        <is>
+          <t>??????</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="0" t="n"/>
+      <c r="F68" s="0" t="n"/>
+      <c r="H68" s="0" t="inlineStr">
+        <is>
+          <t>HumanArmar</t>
+        </is>
+      </c>
+      <c r="J68" s="0" t="n">
+        <v>59</v>
+      </c>
+      <c r="K68" s="0" t="inlineStr">
+        <is>
+          <t>??????</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="0" t="n"/>
+      <c r="F69" s="0" t="n"/>
+      <c r="H69" s="0" t="inlineStr">
+        <is>
+          <t>ArmarHead</t>
+        </is>
+      </c>
+      <c r="J69" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="K69" s="0" t="inlineStr">
+        <is>
+          <t>?????</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="0" t="n"/>
+      <c r="F70" s="0" t="n"/>
+      <c r="H70" s="0" t="inlineStr">
+        <is>
+          <t>ArmarChest</t>
+        </is>
+      </c>
+      <c r="J70" s="0" t="n">
+        <v>61</v>
+      </c>
+      <c r="K70" s="0" t="inlineStr">
+        <is>
+          <t>?????</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="0" t="n"/>
+      <c r="F71" s="0" t="n"/>
+      <c r="H71" s="0" t="inlineStr">
+        <is>
+          <t>ArmarHand</t>
+        </is>
+      </c>
+      <c r="J71" s="0" t="n">
+        <v>62</v>
+      </c>
+      <c r="K71" s="0" t="inlineStr">
+        <is>
+          <t>?????</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="0" t="n"/>
+      <c r="F72" s="0" t="n"/>
+      <c r="H72" s="0" t="inlineStr">
+        <is>
+          <t>ArmarLeg</t>
+        </is>
+      </c>
+      <c r="J72" s="0" t="n">
+        <v>63</v>
+      </c>
+      <c r="K72" s="0" t="inlineStr">
+        <is>
+          <t>?????</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="0" t="n"/>
+      <c r="F73" s="0" t="n"/>
+      <c r="H73" s="0" t="inlineStr">
+        <is>
+          <t>ArmarFoot</t>
+        </is>
+      </c>
+      <c r="J73" s="0" t="n">
+        <v>64</v>
+      </c>
+      <c r="K73" s="0" t="inlineStr">
+        <is>
+          <t>?????</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="0" t="n"/>
+      <c r="F74" s="0" t="n"/>
+      <c r="H74" s="0" t="inlineStr">
+        <is>
+          <t>ArmarAccessory</t>
+        </is>
+      </c>
+      <c r="J74" s="0" t="n">
+        <v>65</v>
+      </c>
+      <c r="K74" s="0" t="inlineStr">
+        <is>
+          <t>?????</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>

--- a/Config/Datas/__enums__.xlsx
+++ b/Config/Datas/__enums__.xlsx
@@ -904,7 +904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L101"/>
+  <dimension ref="A1:L107"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="19" customWidth="1" style="1" min="2" max="2"/>
@@ -3412,6 +3412,106 @@
         </is>
       </c>
     </row>
+    <row r="102">
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>demo.ECommonGrade</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>通用品级</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>未指定</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="J103" t="n">
+        <v>1</v>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>凡品</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="J104" t="n">
+        <v>2</v>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>良品</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="J105" t="n">
+        <v>3</v>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>稀品</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="J106" t="n">
+        <v>4</v>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>上品</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="J107" t="n">
+        <v>5</v>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>极品</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
